--- a/基本設計/05_従業員と部門_画面基本設計書.xlsx
+++ b/基本設計/05_従業員と部門_画面基本設計書.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Ref212ad0442444a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rcffcda457e424852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R505fc310fea84e87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rf763cf9bf8f94ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rfaa93cac3ac547ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R6010d7d588e44649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-003_従業員一覧" sheetId="19" r:id="R78818c12ad904c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-004_従業員登録" sheetId="20" r:id="Re2009b3c70ef494e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-005_従業員編集" sheetId="21" r:id="R676a8c4e2770462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-006_従業員詳細" sheetId="22" r:id="Ra046f1f084e242d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-007_部門管理" sheetId="23" r:id="R12b8a94570bb4d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R3f0b1afb09664816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rddac3897fbc54319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R21a6dc3782a14b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R7a2c2d77f808437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R6837a4ab25294491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R28bb0b3e0de94736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-003_従業員一覧" sheetId="19" r:id="R767a0cbf814a4a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-004_従業員登録" sheetId="20" r:id="Rc4f298c30c3b4645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-005_従業員編集" sheetId="21" r:id="R5b77444a64ac4dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-006_従業員詳細" sheetId="22" r:id="Rd1e8186ccb5d4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-007_部門管理" sheetId="23" r:id="Rdc5636cdf8b144a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1690,10 +1690,7 @@
       <x:c r="F16" s="300"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1708,25 +1705,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="343" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="343"/>
-      <x:c r="D19" s="343"/>
-      <x:c r="E19" s="343"/>
-      <x:c r="F19" s="343"/>
-      <x:c r="G19" s="343"/>
-      <x:c r="H19" s="343"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="343"/>
-      <x:c r="C20" s="343"/>
-      <x:c r="D20" s="343"/>
-      <x:c r="E20" s="343"/>
-      <x:c r="F20" s="343"/>
-      <x:c r="G20" s="343"/>
-      <x:c r="H20" s="343"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="343"/>
@@ -3374,54 +3368,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5533,54 +5495,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11659,54 +11589,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13271,54 +13169,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14832,54 +14698,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/基本設計/05_従業員と部門_画面基本設計書.xlsx
+++ b/基本設計/05_従業員と部門_画面基本設計書.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rac9604a8e5b64f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rcea9357348cc4edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rd7e0b23257fb46c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Rddb6de4b137a4448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-003_従業員一覧" sheetId="19" r:id="R9e7d46810f364b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-004_従業員登録" sheetId="20" r:id="R4ec3359e30de4cb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-005_従業員編集" sheetId="21" r:id="Ra1aae921a16b49c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-006_従業員詳細" sheetId="22" r:id="R969c37ece1cc4ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-007_部門管理" sheetId="23" r:id="Rc594cd9ee2564bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_対象画面INDEX" sheetId="24" r:id="R556929a5058d4aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R950f6aefa5044916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb81e254a76764d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R5916a3c920964b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Ra6968d0975d04c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-003_従業員一覧" sheetId="19" r:id="Rf22ba5deb9874b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-004_従業員登録" sheetId="20" r:id="R9289438693e24e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-005_従業員編集" sheetId="21" r:id="R76bbaee6831147c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-006_従業員詳細" sheetId="22" r:id="R10106c6b679a4129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-007_部門管理" sheetId="23" r:id="Rb8ab5bfbf7f04a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_対象画面INDEX" sheetId="24" r:id="Re9e3be34176e4f70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1932,7 +1932,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="344" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1969,7 +1969,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="379" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E13" s="300"/>
       <x:c r="F13" s="300"/>
@@ -1987,7 +1987,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="379" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="E14" s="300"/>
       <x:c r="F14" s="300"/>
@@ -2330,7 +2330,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="382" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-10-15    Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="228"/>
       <x:c r="C4" s="228"/>
@@ -2780,6 +2780,32 @@
       </x:c>
       <x:c r="H20" s="381" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="381" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B21" s="381" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C21" s="381" t="str">
+        <x:v>SCR-003 Excel出力0件時のHTTP 204とMessage表示を明記。</x:v>
+      </x:c>
+      <x:c r="D21" s="381" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E21" s="381" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F21" s="381" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G21" s="381" t="str">
+        <x:v>変更承認待ち</x:v>
+      </x:c>
+      <x:c r="H21" s="381" t="str">
+        <x:v>API-EMP-007の0件HTTP契約を明確化。Baseline IDは変更しない。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6732,7 +6758,7 @@
         <x:v>現在条件・権限範囲の全件を社員番号昇順で出力</x:v>
       </x:c>
       <x:c r="F13" s="232" t="str">
-        <x:v>0件はFile未生成+MSG-I-011。50000件超は条件絞込案内</x:v>
+        <x:v>0件はAPI-EMP-007がHTTP 204 No Content（Body／Fileなし）を返し、SCR-003でMSG-I-011を表示。50000件超は条件絞込案内</x:v>
       </x:c>
       <x:c r="G13" s="232" t="str">
         <x:v>二重Click防止</x:v>
